--- a/artfynd/A 20051-2024 artfynd.xlsx
+++ b/artfynd/A 20051-2024 artfynd.xlsx
@@ -946,10 +946,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117766610</v>
+        <v>117766334</v>
       </c>
       <c r="B4" t="n">
-        <v>100114</v>
+        <v>100116</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>534944</v>
       </c>
       <c r="R4" t="n">
-        <v>6865906</v>
+        <v>6865909</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1057,10 +1057,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>117766334</v>
+        <v>117766610</v>
       </c>
       <c r="B5" t="n">
-        <v>100114</v>
+        <v>100116</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>534944</v>
       </c>
       <c r="R5" t="n">
-        <v>6865909</v>
+        <v>6865906</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
